--- a/data/projected_effort.xlsx
+++ b/data/projected_effort.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://doimspp-my.sharepoint.com/personal/colleen_keefer_fws_gov/Documents/Desktop/Automation tool github/Implementation_Planning/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="8_{E8B67BDC-2A15-4B69-8CE7-68D174EE1FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D41A1B9F-E28F-4936-9F20-85DB3DCF0819}"/>
+  <xr:revisionPtr revIDLastSave="99" documentId="8_{E8B67BDC-2A15-4B69-8CE7-68D174EE1FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E39D98B0-BA49-46A9-8C11-2EA83205D16A}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="2835" windowWidth="29040" windowHeight="15720" xr2:uid="{6ACA3146-90F7-463A-8DB8-CF9C56339AC4}"/>
+    <workbookView xWindow="41055" yWindow="5055" windowWidth="22980" windowHeight="11610" xr2:uid="{6ACA3146-90F7-463A-8DB8-CF9C56339AC4}"/>
   </bookViews>
   <sheets>
     <sheet name="projected_effort" sheetId="1" r:id="rId1"/>
@@ -687,10 +687,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1110,7 +1106,7 @@
         <v>40</v>
       </c>
       <c r="J2">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -1160,7 +1156,7 @@
         <v>60</v>
       </c>
       <c r="J3">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -1210,7 +1206,7 @@
         <v>40</v>
       </c>
       <c r="J4">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -1260,7 +1256,7 @@
         <v>40</v>
       </c>
       <c r="J5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -1310,7 +1306,7 @@
         <v>40</v>
       </c>
       <c r="J6">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>10</v>
@@ -1365,10 +1361,10 @@
         <v>21</v>
       </c>
       <c r="B8">
-        <v>43.2648911</v>
+        <v>43.251815000000001</v>
       </c>
       <c r="C8">
-        <v>-76.98096074</v>
+        <v>-76.960001000000005</v>
       </c>
       <c r="D8" t="s">
         <v>15</v>
@@ -1384,9 +1380,6 @@
       </c>
       <c r="H8" t="s">
         <v>13</v>
-      </c>
-      <c r="J8">
-        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
@@ -1440,9 +1433,6 @@
       <c r="H10" t="s">
         <v>13</v>
       </c>
-      <c r="J10">
-        <v>15</v>
-      </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -1521,9 +1511,6 @@
       <c r="H13" t="s">
         <v>13</v>
       </c>
-      <c r="J13">
-        <v>15</v>
-      </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -1640,10 +1627,10 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>43.464136000000003</v>
+        <v>43.463628999999997</v>
       </c>
       <c r="C18">
-        <v>-76.521203</v>
+        <v>-76.520600000000002</v>
       </c>
       <c r="D18" t="s">
         <v>15</v>
@@ -1661,7 +1648,7 @@
         <v>29</v>
       </c>
       <c r="J18">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
@@ -1724,10 +1711,10 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <v>43.265535999999997</v>
+        <v>43.251815000000001</v>
       </c>
       <c r="C21">
-        <v>-76.967893000000004</v>
+        <v>-76.960001000000005</v>
       </c>
       <c r="D21" t="s">
         <v>15</v>
@@ -1800,7 +1787,7 @@
         <v>29</v>
       </c>
       <c r="J23">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
@@ -1829,7 +1816,7 @@
         <v>29</v>
       </c>
       <c r="J24">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
@@ -1936,7 +1923,7 @@
         <v>29</v>
       </c>
       <c r="J28">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">

--- a/data/projected_effort.xlsx
+++ b/data/projected_effort.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://doimspp-my.sharepoint.com/personal/colleen_keefer_fws_gov/Documents/Desktop/Automation tool github/Implementation_Planning/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://doimspp-my.sharepoint.com/personal/jacob_cochran_fws_gov/Documents/Early Detection Monitoring/Implementation_Planning/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="99" documentId="8_{E8B67BDC-2A15-4B69-8CE7-68D174EE1FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E39D98B0-BA49-46A9-8C11-2EA83205D16A}"/>
+  <xr:revisionPtr revIDLastSave="127" documentId="8_{E8B67BDC-2A15-4B69-8CE7-68D174EE1FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{583AE623-13C2-4459-90DA-C169C92BFCF2}"/>
   <bookViews>
-    <workbookView xWindow="41055" yWindow="5055" windowWidth="22980" windowHeight="11610" xr2:uid="{6ACA3146-90F7-463A-8DB8-CF9C56339AC4}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{6ACA3146-90F7-463A-8DB8-CF9C56339AC4}"/>
   </bookViews>
   <sheets>
     <sheet name="projected_effort" sheetId="1" r:id="rId1"/>
@@ -1007,27 +1007,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{954594C5-8BE9-4471-9822-FA3B98D60D86}">
   <dimension ref="A1:P30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.88671875" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1077,7 +1077,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1177,7 +1177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -1227,7 +1227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -1277,7 +1277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -1332,10 +1332,10 @@
         <v>11</v>
       </c>
       <c r="E7">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="F7">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G7" t="s">
         <v>19</v>
@@ -1356,7 +1356,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1370,10 +1370,10 @@
         <v>15</v>
       </c>
       <c r="E8">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F8">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G8" t="s">
         <v>19</v>
@@ -1382,7 +1382,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -1396,10 +1396,10 @@
         <v>15</v>
       </c>
       <c r="E9">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F9">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G9" t="s">
         <v>23</v>
@@ -1408,7 +1408,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -1500,10 +1500,10 @@
         <v>11</v>
       </c>
       <c r="E13">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F13">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="G13" t="s">
         <v>23</v>
@@ -1512,7 +1512,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -1526,10 +1526,10 @@
         <v>15</v>
       </c>
       <c r="E14">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="F14">
-        <v>189</v>
+        <v>112</v>
       </c>
       <c r="G14" t="s">
         <v>23</v>
@@ -1538,7 +1538,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -1567,7 +1567,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -1596,7 +1596,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -1610,10 +1610,10 @@
         <v>15</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="F17">
-        <v>16</v>
+        <v>145</v>
       </c>
       <c r="G17" t="s">
         <v>23</v>
@@ -1622,7 +1622,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -1706,7 +1706,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -1735,7 +1735,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1761,7 +1761,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -1790,7 +1790,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -1819,7 +1819,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1833,10 +1833,10 @@
         <v>11</v>
       </c>
       <c r="E25">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F25">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="G25" t="s">
         <v>12</v>
@@ -1845,7 +1845,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -1859,10 +1859,10 @@
         <v>15</v>
       </c>
       <c r="E26">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="F26">
-        <v>189</v>
+        <v>112</v>
       </c>
       <c r="G26" t="s">
         <v>12</v>
@@ -1880,7 +1880,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -1893,6 +1893,12 @@
       <c r="D27" t="s">
         <v>15</v>
       </c>
+      <c r="E27">
+        <v>118</v>
+      </c>
+      <c r="F27">
+        <v>131</v>
+      </c>
       <c r="G27" t="s">
         <v>12</v>
       </c>
@@ -1903,7 +1909,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -1916,6 +1922,12 @@
       <c r="D28" t="s">
         <v>15</v>
       </c>
+      <c r="E28">
+        <v>107</v>
+      </c>
+      <c r="F28">
+        <v>109</v>
+      </c>
       <c r="G28" t="s">
         <v>12</v>
       </c>
@@ -1926,7 +1938,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>34</v>
       </c>
@@ -1939,6 +1951,12 @@
       <c r="D29" t="s">
         <v>15</v>
       </c>
+      <c r="E29">
+        <v>210</v>
+      </c>
+      <c r="F29">
+        <v>206</v>
+      </c>
       <c r="G29" t="s">
         <v>23</v>
       </c>
@@ -1946,7 +1964,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>35</v>
       </c>
@@ -1958,6 +1976,12 @@
       </c>
       <c r="D30" t="s">
         <v>15</v>
+      </c>
+      <c r="E30">
+        <v>116</v>
+      </c>
+      <c r="F30">
+        <v>107</v>
       </c>
       <c r="G30" t="s">
         <v>23</v>

--- a/data/projected_effort.xlsx
+++ b/data/projected_effort.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://doimspp-my.sharepoint.com/personal/jacob_cochran_fws_gov/Documents/Early Detection Monitoring/Implementation_Planning/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="127" documentId="8_{E8B67BDC-2A15-4B69-8CE7-68D174EE1FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{583AE623-13C2-4459-90DA-C169C92BFCF2}"/>
+  <xr:revisionPtr revIDLastSave="191" documentId="8_{E8B67BDC-2A15-4B69-8CE7-68D174EE1FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D7F2D50-BB6D-4261-86EB-F4B165CFD87D}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{6ACA3146-90F7-463A-8DB8-CF9C56339AC4}"/>
   </bookViews>
   <sheets>
     <sheet name="projected_effort" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="43">
   <si>
     <t>Location</t>
   </si>
@@ -79,9 +92,6 @@
     <t>North Tonawanda, NY</t>
   </si>
   <si>
-    <t>Moderate</t>
-  </si>
-  <si>
     <t>Upper Niagara River, NY/ON</t>
   </si>
   <si>
@@ -106,9 +116,6 @@
     <t>Cattaragaus Creek, NY</t>
   </si>
   <si>
-    <t>Massena, NY/ON</t>
-  </si>
-  <si>
     <t>Targeted</t>
   </si>
   <si>
@@ -146,6 +153,15 @@
   </si>
   <si>
     <t>Sweep Net</t>
+  </si>
+  <si>
+    <t>Black River Bay, NY</t>
+  </si>
+  <si>
+    <t>Lake St. Lawrence, NY/ON</t>
+  </si>
+  <si>
+    <t>Lake St. Francis, NY/ON</t>
   </si>
 </sst>
 </file>
@@ -1006,7 +1022,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{954594C5-8BE9-4471-9822-FA3B98D60D86}">
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" bestFit="1" customWidth="1"/>
@@ -1017,7 +1033,7 @@
     <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.42578125" bestFit="1" customWidth="1"/>
@@ -1041,10 +1057,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G1" t="s">
         <v>4</v>
@@ -1065,16 +1081,16 @@
         <v>9</v>
       </c>
       <c r="M1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O1" t="s">
         <v>38</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>39</v>
-      </c>
-      <c r="O1" t="s">
-        <v>40</v>
-      </c>
-      <c r="P1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -1103,6 +1119,7 @@
         <v>13</v>
       </c>
       <c r="I2">
+        <f>SUM(L2:N2)</f>
         <v>40</v>
       </c>
       <c r="J2">
@@ -1115,10 +1132,10 @@
         <v>20</v>
       </c>
       <c r="M2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -1153,6 +1170,7 @@
         <v>13</v>
       </c>
       <c r="I3">
+        <f t="shared" ref="I3:I7" si="0">SUM(L3:N3)</f>
         <v>60</v>
       </c>
       <c r="J3">
@@ -1203,6 +1221,7 @@
         <v>13</v>
       </c>
       <c r="I4">
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="J4">
@@ -1215,10 +1234,10 @@
         <v>20</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -1247,12 +1266,13 @@
         <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="H5" t="s">
         <v>13</v>
       </c>
       <c r="I5">
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="J5">
@@ -1265,10 +1285,10 @@
         <v>20</v>
       </c>
       <c r="M5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -1297,22 +1317,23 @@
         <v>46</v>
       </c>
       <c r="G6" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H6" t="s">
         <v>13</v>
       </c>
       <c r="I6">
-        <v>40</v>
+        <f t="shared" si="0"/>
+        <v>30</v>
       </c>
       <c r="J6">
         <v>10</v>
       </c>
       <c r="L6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>10</v>
@@ -1320,7 +1341,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>43.027583540000002</v>
@@ -1338,27 +1359,28 @@
         <v>61</v>
       </c>
       <c r="G7" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H7" t="s">
         <v>13</v>
       </c>
       <c r="I7">
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="J7">
         <v>20</v>
       </c>
       <c r="L7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M7">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>43.251815000000001</v>
@@ -1376,7 +1398,7 @@
         <v>58</v>
       </c>
       <c r="G8" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H8" t="s">
         <v>13</v>
@@ -1384,7 +1406,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>44.250826000000004</v>
@@ -1402,15 +1424,18 @@
         <v>64</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H9" t="s">
         <v>13</v>
       </c>
+      <c r="J9">
+        <v>30</v>
+      </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10">
         <v>42.487721780000001</v>
@@ -1428,15 +1453,18 @@
         <v>77</v>
       </c>
       <c r="G10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H10" t="s">
         <v>13</v>
       </c>
+      <c r="J10">
+        <v>10</v>
+      </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11">
         <v>43.233587</v>
@@ -1454,7 +1482,7 @@
         <v>86</v>
       </c>
       <c r="G11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H11" t="s">
         <v>13</v>
@@ -1462,7 +1490,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B12">
         <v>43.364257000000002</v>
@@ -1480,7 +1508,7 @@
         <v>101</v>
       </c>
       <c r="G12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H12" t="s">
         <v>13</v>
@@ -1488,7 +1516,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B13">
         <v>42.567559340000003</v>
@@ -1506,7 +1534,7 @@
         <v>134</v>
       </c>
       <c r="G13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H13" t="s">
         <v>13</v>
@@ -1514,25 +1542,25 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="B14">
-        <v>45.002239000000003</v>
+        <v>44.910923979121897</v>
       </c>
       <c r="C14">
-        <v>-74.792409000000006</v>
+        <v>-75.116843413566698</v>
       </c>
       <c r="D14" t="s">
         <v>15</v>
       </c>
       <c r="E14">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="F14">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="G14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H14" t="s">
         <v>13</v>
@@ -1540,112 +1568,112 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="B15">
-        <v>42.875659810000002</v>
+        <v>44.989308091740398</v>
       </c>
       <c r="C15">
-        <v>-78.875949579999997</v>
+        <v>-74.740341342397102</v>
       </c>
       <c r="D15" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="F15">
-        <v>8</v>
+        <v>112</v>
       </c>
       <c r="G15" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H15" t="s">
-        <v>29</v>
-      </c>
-      <c r="J15">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="B16">
-        <v>43.253931999999999</v>
+        <v>43.969969920031197</v>
       </c>
       <c r="C16">
-        <v>-77.573269999999994</v>
+        <v>-76.108388104891603</v>
       </c>
       <c r="D16" t="s">
         <v>15</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>87</v>
       </c>
       <c r="F16">
-        <v>16</v>
+        <v>127</v>
       </c>
       <c r="G16" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H16" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="J16">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="B17">
-        <v>43.307336999999997</v>
+        <v>42.875659810000002</v>
       </c>
       <c r="C17">
-        <v>-77.717062999999996</v>
+        <v>-78.875949579999997</v>
       </c>
       <c r="D17" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E17">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="F17">
-        <v>145</v>
+        <v>8</v>
       </c>
       <c r="G17" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H17" t="s">
-        <v>29</v>
+        <v>27</v>
+      </c>
+      <c r="J17">
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18">
+        <v>43.253931999999999</v>
+      </c>
+      <c r="C18">
+        <v>-77.573269999999994</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18">
+        <v>5</v>
+      </c>
+      <c r="F18">
         <v>16</v>
       </c>
-      <c r="B18">
-        <v>43.463628999999997</v>
-      </c>
-      <c r="C18">
-        <v>-76.520600000000002</v>
-      </c>
-      <c r="D18" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18">
-        <v>6</v>
-      </c>
-      <c r="F18">
-        <v>22</v>
-      </c>
       <c r="G18" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="H18" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J18">
         <v>10</v>
@@ -1653,54 +1681,54 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B19">
-        <v>42.136245520000003</v>
+        <v>43.307336999999997</v>
       </c>
       <c r="C19">
-        <v>-80.099798649999997</v>
+        <v>-77.717062999999996</v>
       </c>
       <c r="D19" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E19">
+        <v>95</v>
+      </c>
+      <c r="F19">
+        <v>145</v>
+      </c>
+      <c r="G19" t="s">
+        <v>22</v>
+      </c>
+      <c r="H19" t="s">
         <v>27</v>
-      </c>
-      <c r="F19">
-        <v>25</v>
-      </c>
-      <c r="G19" t="s">
-        <v>19</v>
-      </c>
-      <c r="H19" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B20">
-        <v>43.035739139999997</v>
+        <v>43.463628999999997</v>
       </c>
       <c r="C20">
-        <v>-78.842143460000003</v>
+        <v>-76.520600000000002</v>
       </c>
       <c r="D20" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E20">
+        <v>6</v>
+      </c>
+      <c r="F20">
+        <v>22</v>
+      </c>
+      <c r="G20" t="s">
         <v>29</v>
       </c>
-      <c r="F20">
-        <v>46</v>
-      </c>
-      <c r="G20" t="s">
-        <v>12</v>
-      </c>
       <c r="H20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J20">
         <v>10</v>
@@ -1708,286 +1736,335 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B21">
-        <v>43.251815000000001</v>
+        <v>42.136245520000003</v>
       </c>
       <c r="C21">
-        <v>-76.960001000000005</v>
+        <v>-80.099798649999997</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E21">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="F21">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="G21" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H21" t="s">
-        <v>29</v>
-      </c>
-      <c r="J21">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B22">
-        <v>42.487721780000001</v>
+        <v>43.035739139999997</v>
       </c>
       <c r="C22">
-        <v>-79.331886679999997</v>
+        <v>-78.842143460000003</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
       </c>
       <c r="E22">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="F22">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="G22" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H22" t="s">
-        <v>29</v>
+        <v>27</v>
+      </c>
+      <c r="J22">
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B23">
-        <v>43.233587</v>
+        <v>43.251815000000001</v>
       </c>
       <c r="C23">
-        <v>-79.054096999999999</v>
+        <v>-76.960001000000005</v>
       </c>
       <c r="D23" t="s">
         <v>15</v>
       </c>
       <c r="E23">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="F23">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="G23" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="H23" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J23">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B24">
-        <v>43.364257000000002</v>
+        <v>42.487721780000001</v>
       </c>
       <c r="C24">
-        <v>-78.192469000000003</v>
+        <v>-79.331886679999997</v>
       </c>
       <c r="D24" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E24">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="F24">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="G24" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="H24" t="s">
-        <v>29</v>
-      </c>
-      <c r="J24">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>43.233587</v>
+      </c>
+      <c r="C25">
+        <v>-79.054096999999999</v>
+      </c>
+      <c r="D25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25">
+        <v>81</v>
+      </c>
+      <c r="F25">
+        <v>86</v>
+      </c>
+      <c r="G25" t="s">
+        <v>29</v>
+      </c>
+      <c r="H25" t="s">
         <v>27</v>
       </c>
-      <c r="B25">
-        <v>42.567559340000003</v>
-      </c>
-      <c r="C25">
-        <v>-79.115413599999997</v>
-      </c>
-      <c r="D25" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25">
-        <v>97</v>
-      </c>
-      <c r="F25">
-        <v>134</v>
-      </c>
-      <c r="G25" t="s">
-        <v>12</v>
-      </c>
-      <c r="H25" t="s">
-        <v>29</v>
+      <c r="J25">
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B26">
-        <v>45.002239000000003</v>
+        <v>43.364257000000002</v>
       </c>
       <c r="C26">
-        <v>-74.792409000000006</v>
+        <v>-78.192469000000003</v>
       </c>
       <c r="D26" t="s">
         <v>15</v>
       </c>
       <c r="E26">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F26">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="G26" t="s">
         <v>12</v>
       </c>
       <c r="H26" t="s">
-        <v>29</v>
-      </c>
-      <c r="I26">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="J26">
-        <v>110</v>
-      </c>
-      <c r="L26">
-        <v>60</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B27">
-        <v>43.33813</v>
+        <v>42.567559340000003</v>
       </c>
       <c r="C27">
-        <v>-78.718518000000003</v>
+        <v>-79.115413599999997</v>
       </c>
       <c r="D27" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E27">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="F27">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G27" t="s">
         <v>12</v>
       </c>
       <c r="H27" t="s">
-        <v>29</v>
-      </c>
-      <c r="J27">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B28">
-        <v>43.569085999999999</v>
+        <v>44.910923979121897</v>
       </c>
       <c r="C28">
-        <v>-76.203276000000002</v>
+        <v>-75.116843413566698</v>
       </c>
       <c r="D28" t="s">
         <v>15</v>
       </c>
       <c r="E28">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="F28">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G28" t="s">
         <v>12</v>
       </c>
       <c r="H28" t="s">
-        <v>29</v>
+        <v>27</v>
+      </c>
+      <c r="I28">
+        <v>60</v>
       </c>
       <c r="J28">
-        <v>10</v>
+        <v>120</v>
+      </c>
+      <c r="L28">
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B29">
-        <v>43.300778999999999</v>
+        <v>43.33813</v>
       </c>
       <c r="C29">
-        <v>-76.836208999999997</v>
+        <v>-78.718518000000003</v>
       </c>
       <c r="D29" t="s">
         <v>15</v>
       </c>
       <c r="E29">
-        <v>210</v>
+        <v>118</v>
       </c>
       <c r="F29">
-        <v>206</v>
+        <v>131</v>
       </c>
       <c r="G29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H29" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B30">
+        <v>43.569085999999999</v>
+      </c>
+      <c r="C30">
+        <v>-76.203276000000002</v>
+      </c>
+      <c r="D30" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30">
+        <v>107</v>
+      </c>
+      <c r="F30">
+        <v>109</v>
+      </c>
+      <c r="G30" t="s">
+        <v>22</v>
+      </c>
+      <c r="H30" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31">
+        <v>43.300778999999999</v>
+      </c>
+      <c r="C31">
+        <v>-76.836208999999997</v>
+      </c>
+      <c r="D31" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31">
+        <v>210</v>
+      </c>
+      <c r="F31">
+        <v>206</v>
+      </c>
+      <c r="G31" t="s">
+        <v>22</v>
+      </c>
+      <c r="H31" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32">
         <v>43.330714999999998</v>
       </c>
-      <c r="C30">
+      <c r="C32">
         <v>-76.705862999999994</v>
       </c>
-      <c r="D30" t="s">
-        <v>15</v>
-      </c>
-      <c r="E30">
+      <c r="D32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32">
         <v>116</v>
       </c>
-      <c r="F30">
+      <c r="F32">
         <v>107</v>
       </c>
-      <c r="G30" t="s">
-        <v>23</v>
-      </c>
-      <c r="H30" t="s">
-        <v>29</v>
+      <c r="G32" t="s">
+        <v>22</v>
+      </c>
+      <c r="H32" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
